--- a/dados/excel/secretaria_cargo.xlsx
+++ b/dados/excel/secretaria_cargo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$G$154</definedName>
@@ -634,7 +634,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10/10/2026 14:55</t>
+          <t>12/10/2026 16:30</t>
         </is>
       </c>
     </row>

--- a/dados/excel/secretaria_cargo.xlsx
+++ b/dados/excel/secretaria_cargo.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026 16:30</t>
+          <t>16/10/2026 19:58</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         <v>6504.32</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="6">
@@ -1355,7 +1355,7 @@
         <v>2572.32</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>95.37</v>
+        <v>95.56</v>
       </c>
     </row>
     <row r="21">
@@ -1382,7 +1382,7 @@
         <v>12503.93</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>96.26000000000001</v>
+        <v>96.33</v>
       </c>
     </row>
     <row r="22">
@@ -1409,7 +1409,7 @@
         <v>4778.01</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>92.67</v>
+        <v>92.78</v>
       </c>
     </row>
     <row r="23">
@@ -1436,7 +1436,7 @@
         <v>4876.53</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>96.59999999999999</v>
+        <v>96.76000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1463,7 +1463,7 @@
         <v>1084.8</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>89.16</v>
+        <v>89.47</v>
       </c>
     </row>
     <row r="25">
@@ -1490,7 +1490,7 @@
         <v>4156.02</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>62.71</v>
+        <v>62.55</v>
       </c>
     </row>
     <row r="26">
@@ -1517,7 +1517,7 @@
         <v>5212.8</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>56.46</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="27">
@@ -1706,7 +1706,7 @@
         <v>14448.13</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>81.81999999999999</v>
+        <v>80.95</v>
       </c>
     </row>
     <row r="34">
@@ -1922,7 +1922,7 @@
         <v>7339.08</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>79.02</v>
+        <v>79.20999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1949,7 +1949,7 @@
         <v>18743.08</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>46.55</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="43">
@@ -1976,7 +1976,7 @@
         <v>13833.87</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>89.14</v>
+        <v>89.43000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -2003,7 +2003,7 @@
         <v>4552.07</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>61.21</v>
+        <v>60.85</v>
       </c>
     </row>
     <row r="45">
@@ -2894,7 +2894,7 @@
         <v>8902.379999999999</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>18.52</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="78">
@@ -3866,7 +3866,7 @@
         <v>7915.79</v>
       </c>
       <c r="G113" s="15" t="n">
-        <v>45.45</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="114">
@@ -4298,7 +4298,7 @@
         <v>6526.29</v>
       </c>
       <c r="G129" s="15" t="n">
-        <v>19.7</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="130">
@@ -4568,7 +4568,7 @@
         <v>4883.2</v>
       </c>
       <c r="G139" s="15" t="n">
-        <v>30.77</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140">
@@ -4649,7 +4649,7 @@
         <v>15452.79</v>
       </c>
       <c r="G142" s="11" t="n">
-        <v>8.33</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="143">
